--- a/default/input_ParameterCosts.xlsx
+++ b/default/input_ParameterCosts.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\atmosphere\default\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\UrbanHeatOpt\default\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB621FD-C3E3-4E6D-94F9-0EFBB90D6B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8608E6A5-0C0F-45A6-890A-11980762C202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
   <si>
     <t>Parameter</t>
   </si>
@@ -178,6 +178,18 @@
   </si>
   <si>
     <t>Allow/restrict decentral heating for buildings connected to the network</t>
+  </si>
+  <si>
+    <t>Time step durration</t>
+  </si>
+  <si>
+    <t>phWeight</t>
+  </si>
+  <si>
+    <t>hour</t>
+  </si>
+  <si>
+    <t>durration of a time step in hours</t>
   </si>
 </sst>
 </file>
@@ -244,12 +256,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -531,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="60.453125" bestFit="1" customWidth="1"/>
@@ -756,7 +770,7 @@
       <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -765,11 +779,28 @@
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="3" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="6">
+        <v>1</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
